--- a/CalendarioEvaluaciones.xlsx
+++ b/CalendarioEvaluaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E494F1-1C2C-4323-93A0-DA282CA2B79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA9D29C-20EE-4484-A1D7-BE22E7E742F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1105,7 +1105,7 @@
     <col min="4" max="4" width="6.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9.28515625" style="2"/>
   </cols>

--- a/CalendarioEvaluaciones.xlsx
+++ b/CalendarioEvaluaciones.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA9D29C-20EE-4484-A1D7-BE22E7E742F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD87C0A4-71E0-404C-8561-0C1E963ED5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -32,9 +32,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -424,7 +421,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -502,9 +499,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -533,16 +527,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -570,13 +554,13 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -590,6 +574,39 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1097,20 +1114,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:O45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="2"/>
-    <col min="2" max="2" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" style="2"/>
+    <col min="2" max="2" width="13.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.28515625" style="2"/>
+    <col min="6" max="6" width="38.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1133,89 +1150,89 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="58">
         <v>0.05</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="59">
         <v>46088</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="60">
         <v>46091</v>
       </c>
-      <c r="G2" s="22"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="61"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="63" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="24" t="s">
+    <row r="3" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="65">
         <v>0.05</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="66">
         <v>46089</v>
       </c>
-      <c r="F3" s="28"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="30">
+      <c r="F3" s="67"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="69">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="31" t="s">
+    <row r="4" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="58">
         <v>0.15</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="59">
         <v>46095</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="22">
+      <c r="F4" s="60"/>
+      <c r="G4" s="61">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="62">
         <v>1</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="63" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="32" t="s">
+    <row r="5" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="65">
         <v>0.1</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="66">
         <v>46096</v>
       </c>
-      <c r="F5" s="28"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="30"/>
-    </row>
-    <row r="6" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F5" s="67"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="69"/>
+    </row>
+    <row r="6" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="17" t="s">
         <v>8</v>
       </c>
@@ -1237,8 +1254,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="32" t="s">
+    <row r="7" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="25" t="s">
@@ -1252,30 +1269,30 @@
       <c r="G7" s="29"/>
       <c r="H7" s="30"/>
     </row>
-    <row r="8" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="33" t="s">
+    <row r="8" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="34">
         <v>0.1</v>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="35">
         <v>46104</v>
       </c>
-      <c r="F8" s="37"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="39" t="s">
+      <c r="F8" s="36"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38" t="s">
         <v>21</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="40" t="s">
+    <row r="9" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="39" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="18" t="s">
@@ -1298,48 +1315,46 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="41" t="s">
+    <row r="10" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="12">
         <v>0.1</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="5">
         <v>46118</v>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="6">
         <v>46124</v>
       </c>
-      <c r="G10" s="45"/>
-      <c r="H10" s="46"/>
-    </row>
-    <row r="11" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="47" t="s">
+      <c r="H10" s="41"/>
+    </row>
+    <row r="11" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="12">
         <v>0.15</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="5">
         <v>46121</v>
       </c>
-      <c r="F11" s="44"/>
-      <c r="G11" s="45">
+      <c r="G11" s="7">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H11" s="46">
+      <c r="H11" s="41">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="32" t="s">
+    <row r="12" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="25" t="s">
@@ -1359,8 +1374,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="40" t="s">
+    <row r="13" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="39" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="18" t="s">
@@ -1384,8 +1399,8 @@
       </c>
       <c r="J13" s="13"/>
     </row>
-    <row r="14" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="48" t="s">
+    <row r="14" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="43" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="25" t="s">
@@ -1404,8 +1419,8 @@
       <c r="H14" s="30"/>
       <c r="J14" s="13"/>
     </row>
-    <row r="15" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="49" t="s">
+    <row r="15" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="44" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="18" t="s">
@@ -1427,28 +1442,27 @@
       </c>
       <c r="J15" s="13"/>
     </row>
-    <row r="16" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="50" t="s">
+    <row r="16" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D16" s="12">
         <v>0.15</v>
       </c>
-      <c r="E16" s="43">
+      <c r="E16" s="5">
         <v>46135</v>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="6">
         <v>46145</v>
       </c>
-      <c r="G16" s="45"/>
-      <c r="H16" s="46"/>
+      <c r="H16" s="41"/>
       <c r="J16" s="13"/>
     </row>
-    <row r="17" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="32" t="s">
+    <row r="17" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="25" t="s">
@@ -1469,29 +1483,29 @@
       </c>
       <c r="J17" s="13"/>
     </row>
-    <row r="18" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="51" t="s">
+    <row r="18" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="34">
         <v>0.15</v>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="35">
         <v>46145</v>
       </c>
-      <c r="F18" s="37"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="39"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="38"/>
       <c r="I18" s="2" t="s">
         <v>37</v>
       </c>
       <c r="J18" s="14"/>
     </row>
-    <row r="19" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="40" t="s">
+    <row r="19" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="39" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="18" t="s">
@@ -1515,8 +1529,8 @@
       </c>
       <c r="J19" s="14"/>
     </row>
-    <row r="20" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="52" t="s">
+    <row r="20" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="47" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="25" t="s">
@@ -1533,8 +1547,8 @@
       <c r="H20" s="30"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="40" t="s">
+    <row r="21" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="39" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="18" t="s">
@@ -1556,50 +1570,48 @@
       </c>
       <c r="J21" s="14"/>
     </row>
-    <row r="22" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="50" t="s">
+    <row r="22" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="42" t="s">
+      <c r="C22" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="12">
         <v>0.1</v>
       </c>
-      <c r="E22" s="43">
+      <c r="E22" s="5">
         <v>46156</v>
       </c>
-      <c r="F22" s="44">
+      <c r="F22" s="6">
         <v>46159</v>
       </c>
-      <c r="G22" s="45"/>
-      <c r="H22" s="46"/>
+      <c r="H22" s="41"/>
       <c r="J22" s="14"/>
     </row>
-    <row r="23" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="53" t="s">
+    <row r="23" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D23" s="12">
         <v>0.1</v>
       </c>
-      <c r="E23" s="43">
+      <c r="E23" s="5">
         <v>46157</v>
       </c>
-      <c r="F23" s="44">
+      <c r="F23" s="6">
         <v>46159</v>
       </c>
-      <c r="G23" s="45"/>
-      <c r="H23" s="46">
+      <c r="H23" s="41">
         <v>2</v>
       </c>
       <c r="J23" s="14"/>
     </row>
-    <row r="24" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="52" t="s">
+    <row r="24" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="47" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="25" t="s">
@@ -1620,8 +1632,8 @@
       </c>
       <c r="J24" s="14"/>
     </row>
-    <row r="25" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="49" t="s">
+    <row r="25" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="44" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="18" t="s">
@@ -1630,7 +1642,7 @@
       <c r="D25" s="19">
         <v>0.2</v>
       </c>
-      <c r="E25" s="54">
+      <c r="E25" s="49">
         <v>46167</v>
       </c>
       <c r="F25" s="21"/>
@@ -1640,24 +1652,23 @@
       </c>
       <c r="J25" s="14"/>
     </row>
-    <row r="26" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="41" t="s">
+    <row r="26" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="42" t="s">
+      <c r="C26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="12">
         <v>0.15</v>
       </c>
-      <c r="E26" s="55">
+      <c r="E26" s="50">
         <v>46167</v>
       </c>
-      <c r="F26" s="44"/>
-      <c r="G26" s="45">
+      <c r="G26" s="7">
         <v>0.875</v>
       </c>
-      <c r="H26" s="46">
+      <c r="H26" s="41">
         <v>2.2999999999999998</v>
       </c>
       <c r="I26" s="2" t="s">
@@ -1665,69 +1676,65 @@
       </c>
       <c r="J26" s="14"/>
     </row>
-    <row r="27" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="47" t="s">
+    <row r="27" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D27" s="12">
         <v>0.1</v>
       </c>
-      <c r="E27" s="43">
+      <c r="E27" s="5">
         <v>46170</v>
       </c>
-      <c r="F27" s="44"/>
-      <c r="G27" s="45">
+      <c r="G27" s="7">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H27" s="46"/>
+      <c r="H27" s="41"/>
       <c r="J27" s="14"/>
       <c r="N27" s="16"/>
     </row>
-    <row r="28" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="50" t="s">
+    <row r="28" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D28" s="12">
         <v>0.25</v>
       </c>
-      <c r="E28" s="43">
+      <c r="E28" s="5">
         <v>46171</v>
       </c>
-      <c r="F28" s="44">
+      <c r="F28" s="6">
         <v>46182</v>
       </c>
-      <c r="G28" s="45"/>
-      <c r="H28" s="46"/>
+      <c r="H28" s="41"/>
       <c r="J28" s="14"/>
     </row>
-    <row r="29" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="56" t="s">
+    <row r="29" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="42" t="s">
+      <c r="C29" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="12">
         <v>0.05</v>
       </c>
-      <c r="E29" s="57">
+      <c r="E29" s="52">
         <v>46173</v>
       </c>
-      <c r="F29" s="44"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="46">
+      <c r="H29" s="41">
         <v>6</v>
       </c>
       <c r="J29" s="14"/>
     </row>
-    <row r="30" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="32" t="s">
+    <row r="30" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="25" t="s">
@@ -1736,7 +1743,7 @@
       <c r="D30" s="26">
         <v>0.1</v>
       </c>
-      <c r="E30" s="58">
+      <c r="E30" s="53">
         <v>46173</v>
       </c>
       <c r="F30" s="28"/>
@@ -1748,8 +1755,8 @@
       </c>
       <c r="J30" s="14"/>
     </row>
-    <row r="31" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="59" t="s">
+    <row r="31" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="54" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="18" t="s">
@@ -1770,30 +1777,28 @@
       </c>
       <c r="J31" s="14"/>
     </row>
-    <row r="32" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="56" t="s">
+    <row r="32" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="42" t="s">
+      <c r="C32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D32" s="15">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E32" s="43">
+      <c r="E32" s="5">
         <v>46180</v>
       </c>
-      <c r="F32" s="44"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="46"/>
+      <c r="H32" s="41"/>
       <c r="I32" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J32" s="14"/>
       <c r="M32" s="16"/>
     </row>
-    <row r="33" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="52" t="s">
+    <row r="33" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="47" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="25" t="s">
@@ -1810,17 +1815,17 @@
       <c r="H33" s="30"/>
       <c r="J33" s="14"/>
     </row>
-    <row r="34" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="49" t="s">
+    <row r="34" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="44" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="60">
+      <c r="D34" s="55">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E34" s="61">
+      <c r="E34" s="56">
         <v>46181</v>
       </c>
       <c r="F34" s="21"/>
@@ -1828,31 +1833,30 @@
       <c r="H34" s="23"/>
       <c r="J34" s="14"/>
     </row>
-    <row r="35" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="41" t="s">
+    <row r="35" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="42" t="s">
+      <c r="C35" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="12">
         <v>0.1</v>
       </c>
-      <c r="E35" s="57">
+      <c r="E35" s="52">
         <v>46181</v>
       </c>
-      <c r="F35" s="44">
+      <c r="F35" s="6">
         <v>46187</v>
       </c>
-      <c r="G35" s="45"/>
-      <c r="H35" s="46"/>
+      <c r="H35" s="41"/>
       <c r="I35" s="2" t="s">
         <v>37</v>
       </c>
       <c r="J35" s="14"/>
     </row>
-    <row r="36" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="52" t="s">
+    <row r="36" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="47" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="25" t="s">
@@ -1873,8 +1877,8 @@
       </c>
       <c r="J36" s="14"/>
     </row>
-    <row r="37" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="49" t="s">
+    <row r="37" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="44" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="18" t="s">
@@ -1894,49 +1898,46 @@
       <c r="J37" s="14"/>
       <c r="O37" s="16"/>
     </row>
-    <row r="38" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="41" t="s">
+    <row r="38" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="C38" s="42" t="s">
+      <c r="C38" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D38" s="12">
         <v>0.15</v>
       </c>
-      <c r="E38" s="43">
+      <c r="E38" s="5">
         <v>46188</v>
       </c>
-      <c r="F38" s="44">
+      <c r="F38" s="6">
         <v>46194</v>
       </c>
-      <c r="G38" s="45"/>
-      <c r="H38" s="46"/>
+      <c r="H38" s="41"/>
       <c r="I38" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="50" t="s">
+    <row r="39" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C39" s="42" t="s">
+      <c r="C39" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D39" s="12">
         <v>0.25</v>
       </c>
-      <c r="E39" s="43">
+      <c r="E39" s="5">
         <v>46189</v>
       </c>
-      <c r="F39" s="44"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="46">
+      <c r="H39" s="41">
         <v>1.6</v>
       </c>
     </row>
-    <row r="40" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="32" t="s">
+    <row r="40" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C40" s="25" t="s">
@@ -1952,8 +1953,8 @@
       <c r="G40" s="29"/>
       <c r="H40" s="30"/>
     </row>
-    <row r="41" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="59" t="s">
+    <row r="41" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="54" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="18" t="s">
@@ -1970,7 +1971,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="24" t="s">
         <v>7</v>
       </c>
@@ -1989,13 +1990,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B43" s="3"/>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B44" s="3"/>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B45" s="3"/>
     </row>
   </sheetData>

--- a/CalendarioEvaluaciones.xlsx
+++ b/CalendarioEvaluaciones.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD87C0A4-71E0-404C-8561-0C1E963ED5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EC0556-7FB4-49FC-A18E-3585A850A64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1114,20 +1117,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:O45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="2"/>
-    <col min="2" max="2" width="13.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" style="2"/>
+    <col min="2" max="2" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.33203125" style="2"/>
+    <col min="6" max="6" width="38.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.28515625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:10" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1150,7 +1153,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="17" t="s">
         <v>8</v>
       </c>
@@ -1172,7 +1175,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="43" t="s">
         <v>7</v>
       </c>
@@ -1191,7 +1194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="17" t="s">
         <v>9</v>
       </c>
@@ -1215,7 +1218,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="43" t="s">
         <v>11</v>
       </c>
@@ -1232,7 +1235,7 @@
       <c r="G5" s="68"/>
       <c r="H5" s="69"/>
     </row>
-    <row r="6" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="17" t="s">
         <v>8</v>
       </c>
@@ -1254,22 +1257,22 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="31" t="s">
+    <row r="7" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27">
+      <c r="D7" s="65"/>
+      <c r="E7" s="66">
         <v>46099</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="30"/>
-    </row>
-    <row r="8" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F7" s="67"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="69"/>
+    </row>
+    <row r="8" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="32" t="s">
         <v>7</v>
       </c>
@@ -1291,7 +1294,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="39" t="s">
         <v>10</v>
       </c>
@@ -1315,7 +1318,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="40" t="s">
         <v>10</v>
       </c>
@@ -1333,7 +1336,7 @@
       </c>
       <c r="H10" s="41"/>
     </row>
-    <row r="11" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="42" t="s">
         <v>9</v>
       </c>
@@ -1353,7 +1356,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="31" t="s">
         <v>11</v>
       </c>
@@ -1374,7 +1377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="39" t="s">
         <v>10</v>
       </c>
@@ -1399,7 +1402,7 @@
       </c>
       <c r="J13" s="13"/>
     </row>
-    <row r="14" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="43" t="s">
         <v>8</v>
       </c>
@@ -1419,7 +1422,7 @@
       <c r="H14" s="30"/>
       <c r="J14" s="13"/>
     </row>
-    <row r="15" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="44" t="s">
         <v>7</v>
       </c>
@@ -1442,7 +1445,7 @@
       </c>
       <c r="J15" s="13"/>
     </row>
-    <row r="16" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="45" t="s">
         <v>8</v>
       </c>
@@ -1461,7 +1464,7 @@
       <c r="H16" s="41"/>
       <c r="J16" s="13"/>
     </row>
-    <row r="17" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="31" t="s">
         <v>11</v>
       </c>
@@ -1483,7 +1486,7 @@
       </c>
       <c r="J17" s="13"/>
     </row>
-    <row r="18" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="46" t="s">
         <v>11</v>
       </c>
@@ -1504,7 +1507,7 @@
       </c>
       <c r="J18" s="14"/>
     </row>
-    <row r="19" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="39" t="s">
         <v>10</v>
       </c>
@@ -1529,7 +1532,7 @@
       </c>
       <c r="J19" s="14"/>
     </row>
-    <row r="20" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="47" t="s">
         <v>9</v>
       </c>
@@ -1547,7 +1550,7 @@
       <c r="H20" s="30"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="39" t="s">
         <v>10</v>
       </c>
@@ -1570,7 +1573,7 @@
       </c>
       <c r="J21" s="14"/>
     </row>
-    <row r="22" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="45" t="s">
         <v>8</v>
       </c>
@@ -1589,7 +1592,7 @@
       <c r="H22" s="41"/>
       <c r="J22" s="14"/>
     </row>
-    <row r="23" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="48" t="s">
         <v>11</v>
       </c>
@@ -1610,7 +1613,7 @@
       </c>
       <c r="J23" s="14"/>
     </row>
-    <row r="24" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="47" t="s">
         <v>9</v>
       </c>
@@ -1632,7 +1635,7 @@
       </c>
       <c r="J24" s="14"/>
     </row>
-    <row r="25" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="44" t="s">
         <v>7</v>
       </c>
@@ -1652,7 +1655,7 @@
       </c>
       <c r="J25" s="14"/>
     </row>
-    <row r="26" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="40" t="s">
         <v>10</v>
       </c>
@@ -1676,7 +1679,7 @@
       </c>
       <c r="J26" s="14"/>
     </row>
-    <row r="27" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="42" t="s">
         <v>9</v>
       </c>
@@ -1696,7 +1699,7 @@
       <c r="J27" s="14"/>
       <c r="N27" s="16"/>
     </row>
-    <row r="28" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="45" t="s">
         <v>8</v>
       </c>
@@ -1715,7 +1718,7 @@
       <c r="H28" s="41"/>
       <c r="J28" s="14"/>
     </row>
-    <row r="29" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="51" t="s">
         <v>7</v>
       </c>
@@ -1733,7 +1736,7 @@
       </c>
       <c r="J29" s="14"/>
     </row>
-    <row r="30" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="31" t="s">
         <v>11</v>
       </c>
@@ -1755,7 +1758,7 @@
       </c>
       <c r="J30" s="14"/>
     </row>
-    <row r="31" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="54" t="s">
         <v>11</v>
       </c>
@@ -1777,7 +1780,7 @@
       </c>
       <c r="J31" s="14"/>
     </row>
-    <row r="32" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="51" t="s">
         <v>7</v>
       </c>
@@ -1797,7 +1800,7 @@
       <c r="J32" s="14"/>
       <c r="M32" s="16"/>
     </row>
-    <row r="33" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="47" t="s">
         <v>9</v>
       </c>
@@ -1815,7 +1818,7 @@
       <c r="H33" s="30"/>
       <c r="J33" s="14"/>
     </row>
-    <row r="34" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="44" t="s">
         <v>7</v>
       </c>
@@ -1833,7 +1836,7 @@
       <c r="H34" s="23"/>
       <c r="J34" s="14"/>
     </row>
-    <row r="35" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="40" t="s">
         <v>10</v>
       </c>
@@ -1855,7 +1858,7 @@
       </c>
       <c r="J35" s="14"/>
     </row>
-    <row r="36" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="47" t="s">
         <v>9</v>
       </c>
@@ -1877,7 +1880,7 @@
       </c>
       <c r="J36" s="14"/>
     </row>
-    <row r="37" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="44" t="s">
         <v>7</v>
       </c>
@@ -1898,7 +1901,7 @@
       <c r="J37" s="14"/>
       <c r="O37" s="16"/>
     </row>
-    <row r="38" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="40" t="s">
         <v>10</v>
       </c>
@@ -1919,7 +1922,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="45" t="s">
         <v>8</v>
       </c>
@@ -1936,7 +1939,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="40" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="31" t="s">
         <v>11</v>
       </c>
@@ -1953,7 +1956,7 @@
       <c r="G40" s="29"/>
       <c r="H40" s="30"/>
     </row>
-    <row r="41" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="54" t="s">
         <v>11</v>
       </c>
@@ -1971,7 +1974,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="24" t="s">
         <v>7</v>
       </c>
@@ -1990,13 +1993,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43" s="3"/>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B44" s="3"/>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B45" s="3"/>
     </row>
   </sheetData>

--- a/CalendarioEvaluaciones.xlsx
+++ b/CalendarioEvaluaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EC0556-7FB4-49FC-A18E-3585A850A64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09508BD7-B20A-444C-8C21-B0B34F4B80E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -169,7 +169,7 @@
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,13 +220,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="12"/>
       <color theme="1"/>
@@ -237,6 +230,29 @@
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,7 +302,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -419,12 +435,65 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -458,12 +527,10 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -483,9 +550,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -502,28 +566,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -533,47 +575,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -611,6 +623,107 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1116,8 +1229,8 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:O45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="26.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="2"/>
     <col min="2" max="2" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -1127,7 +1240,9 @@
     <col min="6" max="6" width="38.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.28515625" style="2"/>
+    <col min="9" max="9" width="9.28515625" style="2"/>
+    <col min="10" max="10" width="9.28515625" style="87"/>
+    <col min="11" max="16384" width="9.28515625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1152,692 +1267,762 @@
       <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="J1" s="82"/>
+    </row>
+    <row r="2" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="58">
+      <c r="D2" s="37">
         <v>0.05</v>
       </c>
-      <c r="E2" s="59">
+      <c r="E2" s="38">
         <v>46088</v>
       </c>
-      <c r="F2" s="60">
+      <c r="F2" s="39">
         <v>46091</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="63" t="s">
+      <c r="G2" s="40"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="42" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="43" t="s">
+      <c r="J2" s="83"/>
+    </row>
+    <row r="3" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="65">
+      <c r="D3" s="44">
         <v>0.05</v>
       </c>
-      <c r="E3" s="66">
+      <c r="E3" s="45">
         <v>46089</v>
       </c>
-      <c r="F3" s="67"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="69">
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="48">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="17" t="s">
+      <c r="J3" s="83"/>
+    </row>
+    <row r="4" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="58">
+      <c r="D4" s="37">
         <v>0.15</v>
       </c>
-      <c r="E4" s="59">
+      <c r="E4" s="38">
         <v>46095</v>
       </c>
-      <c r="F4" s="60"/>
-      <c r="G4" s="61">
+      <c r="F4" s="39"/>
+      <c r="G4" s="40">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H4" s="62">
+      <c r="H4" s="41">
         <v>1</v>
       </c>
-      <c r="I4" s="63" t="s">
+      <c r="I4" s="42" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="43" t="s">
+      <c r="J4" s="83"/>
+    </row>
+    <row r="5" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="65">
+      <c r="D5" s="44">
         <v>0.1</v>
       </c>
-      <c r="E5" s="66">
+      <c r="E5" s="45">
         <v>46096</v>
       </c>
-      <c r="F5" s="67"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="69"/>
-    </row>
-    <row r="6" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17" t="s">
+      <c r="F5" s="46"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="48"/>
+      <c r="J5" s="83"/>
+    </row>
+    <row r="6" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="37">
         <v>0.1</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="38">
         <v>46097</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="39">
         <v>46110</v>
       </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="2" t="s">
+      <c r="G6" s="40"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="42" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="2:10" s="63" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="43" t="s">
+      <c r="J6" s="83"/>
+    </row>
+    <row r="7" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="65"/>
-      <c r="E7" s="66">
+      <c r="D7" s="44"/>
+      <c r="E7" s="45">
         <v>46099</v>
       </c>
-      <c r="F7" s="67"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="69"/>
-    </row>
-    <row r="8" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="32" t="s">
+      <c r="F7" s="46"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="48"/>
+      <c r="J7" s="83"/>
+    </row>
+    <row r="8" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="51">
         <v>0.1</v>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="52">
         <v>46104</v>
       </c>
-      <c r="F8" s="36"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38" t="s">
+      <c r="F8" s="53"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="42" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="39" t="s">
+      <c r="J8" s="83"/>
+    </row>
+    <row r="9" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="37">
         <v>0.1</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="38">
         <v>46118</v>
       </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="22">
+      <c r="F9" s="39"/>
+      <c r="G9" s="40">
         <v>0.875</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="41">
         <v>1</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="42" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="10" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="40" t="s">
+      <c r="J9" s="83"/>
+    </row>
+    <row r="10" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="56">
         <v>0.1</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="57">
         <v>46118</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="58">
         <v>46124</v>
       </c>
-      <c r="H10" s="41"/>
-    </row>
-    <row r="11" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="42" t="s">
+      <c r="G10" s="59"/>
+      <c r="H10" s="60"/>
+      <c r="J10" s="83"/>
+    </row>
+    <row r="11" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="56">
         <v>0.15</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="64">
         <v>46121</v>
       </c>
-      <c r="G11" s="7">
+      <c r="F11" s="66"/>
+      <c r="G11" s="68">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="60">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J11" s="83"/>
+    </row>
+    <row r="12" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B12" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="44">
         <v>0.15</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="45">
         <v>46124</v>
       </c>
-      <c r="F12" s="28"/>
-      <c r="G12" s="29">
+      <c r="F12" s="46"/>
+      <c r="G12" s="47">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="48">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="39" t="s">
+      <c r="J12" s="83"/>
+    </row>
+    <row r="13" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="37">
         <v>0.15</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="38">
         <v>46125</v>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="22">
+      <c r="F13" s="39"/>
+      <c r="G13" s="40">
         <v>0.875</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="41">
         <v>1</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="13"/>
-    </row>
-    <row r="14" spans="2:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="43" t="s">
+      <c r="J13" s="84"/>
+    </row>
+    <row r="14" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="44">
         <v>0.1</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="45">
         <v>46128</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="46">
         <v>46131</v>
       </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="30"/>
-      <c r="J14" s="13"/>
-    </row>
-    <row r="15" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="44" t="s">
+      <c r="G14" s="47"/>
+      <c r="H14" s="48"/>
+      <c r="J14" s="84"/>
+    </row>
+    <row r="15" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="37">
         <v>0.2</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="38">
         <v>46132</v>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="23">
+      <c r="F15" s="39"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41">
         <v>3</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="J15" s="13"/>
-    </row>
-    <row r="16" spans="2:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="45" t="s">
+      <c r="J15" s="84"/>
+    </row>
+    <row r="16" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="56">
         <v>0.15</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="57">
         <v>46135</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="58">
         <v>46145</v>
       </c>
-      <c r="H16" s="41"/>
-      <c r="J16" s="13"/>
-    </row>
-    <row r="17" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G16" s="59"/>
+      <c r="H16" s="60"/>
+      <c r="J16" s="84"/>
+    </row>
+    <row r="17" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B17" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="44">
         <v>0.1</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="45">
         <v>46137</v>
       </c>
-      <c r="F17" s="28"/>
-      <c r="G17" s="29">
+      <c r="F17" s="46"/>
+      <c r="G17" s="47">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="48">
         <v>1.3</v>
       </c>
-      <c r="J17" s="13"/>
-    </row>
-    <row r="18" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="46" t="s">
+      <c r="J17" s="84"/>
+    </row>
+    <row r="18" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="51">
         <v>0.15</v>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="52">
         <v>46145</v>
       </c>
-      <c r="F18" s="36"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="2" t="s">
+      <c r="F18" s="53"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="J18" s="14"/>
-    </row>
-    <row r="19" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="39" t="s">
+      <c r="J18" s="85"/>
+    </row>
+    <row r="19" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="37">
         <v>0.1</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="38">
         <v>46146</v>
       </c>
-      <c r="F19" s="21"/>
-      <c r="G19" s="22">
+      <c r="F19" s="39"/>
+      <c r="G19" s="40">
         <v>0.875</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="41">
         <v>2</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="J19" s="14"/>
-    </row>
-    <row r="20" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="47" t="s">
+      <c r="J19" s="85"/>
+    </row>
+    <row r="20" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B20" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="44">
         <v>0.05</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="45">
         <v>46151</v>
       </c>
-      <c r="F20" s="28"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="30"/>
-      <c r="J20" s="13"/>
-    </row>
-    <row r="21" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="39" t="s">
+      <c r="F20" s="46"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="48"/>
+      <c r="J20" s="84"/>
+    </row>
+    <row r="21" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="37">
         <v>0.15</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="38">
         <v>46153</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="39">
         <v>46159</v>
       </c>
-      <c r="G21" s="22"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="2" t="s">
+      <c r="G21" s="40"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="J21" s="14"/>
-    </row>
-    <row r="22" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="45" t="s">
+      <c r="J21" s="85"/>
+    </row>
+    <row r="22" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="56">
         <v>0.1</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="57">
         <v>46156</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="58">
         <v>46159</v>
       </c>
-      <c r="H22" s="41"/>
-      <c r="J22" s="14"/>
-    </row>
-    <row r="23" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="48" t="s">
+      <c r="G22" s="59"/>
+      <c r="H22" s="60"/>
+      <c r="J22" s="85"/>
+    </row>
+    <row r="23" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="56">
         <v>0.1</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="64">
         <v>46157</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="66">
         <v>46159</v>
       </c>
-      <c r="H23" s="41">
+      <c r="G23" s="68"/>
+      <c r="H23" s="60">
         <v>2</v>
       </c>
-      <c r="J23" s="14"/>
-    </row>
-    <row r="24" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="47" t="s">
+      <c r="J23" s="85"/>
+    </row>
+    <row r="24" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="44">
         <v>0.2</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="45">
         <v>46158</v>
       </c>
-      <c r="F24" s="28"/>
-      <c r="G24" s="29">
+      <c r="F24" s="46"/>
+      <c r="G24" s="47">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="48">
         <v>3</v>
       </c>
-      <c r="J24" s="14"/>
-    </row>
-    <row r="25" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="44" t="s">
+      <c r="J24" s="85"/>
+    </row>
+    <row r="25" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="37">
         <v>0.2</v>
       </c>
-      <c r="E25" s="49">
+      <c r="E25" s="61">
         <v>46167</v>
       </c>
-      <c r="F25" s="21"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="23">
+      <c r="F25" s="39"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="41">
         <v>4.5</v>
       </c>
-      <c r="J25" s="14"/>
-    </row>
-    <row r="26" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="J25" s="85"/>
+    </row>
+    <row r="26" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="42"/>
+      <c r="B26" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="12">
-        <v>0.15</v>
-      </c>
-      <c r="E26" s="50">
-        <v>46167</v>
-      </c>
-      <c r="G26" s="7">
-        <v>0.875</v>
-      </c>
-      <c r="H26" s="41">
-        <v>2.2999999999999998</v>
-      </c>
+      <c r="D26" s="56">
+        <v>0.1</v>
+      </c>
+      <c r="E26" s="64">
+        <v>46170</v>
+      </c>
+      <c r="F26" s="66"/>
+      <c r="G26" s="68">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H26" s="60"/>
       <c r="I26" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J26" s="14"/>
-    </row>
-    <row r="27" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="J26" s="86"/>
+    </row>
+    <row r="27" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="2"/>
+      <c r="B27" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="E27" s="70">
+        <v>46171</v>
+      </c>
+      <c r="F27" s="67">
+        <v>46182</v>
+      </c>
+      <c r="G27" s="69"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="87">
+        <v>7</v>
+      </c>
+      <c r="L27" s="87"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+    </row>
+    <row r="28" spans="1:20" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B28" s="81" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="E28" s="65">
+        <v>46173</v>
+      </c>
+      <c r="F28" s="67">
+        <v>46180</v>
+      </c>
+      <c r="G28" s="69"/>
+      <c r="H28" s="30">
+        <v>6</v>
+      </c>
+      <c r="J28" s="87">
+        <v>2</v>
+      </c>
+      <c r="K28" s="87"/>
+      <c r="L28" s="87"/>
+    </row>
+    <row r="29" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D29" s="17">
         <v>0.1</v>
       </c>
-      <c r="E27" s="5">
-        <v>46170</v>
-      </c>
-      <c r="G27" s="7">
+      <c r="E29" s="35">
+        <v>46176</v>
+      </c>
+      <c r="F29" s="19"/>
+      <c r="G29" s="20">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H27" s="41"/>
-      <c r="J27" s="14"/>
-      <c r="N27" s="16"/>
-    </row>
-    <row r="28" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="E28" s="5">
-        <v>46171</v>
-      </c>
-      <c r="F28" s="6">
-        <v>46182</v>
-      </c>
-      <c r="H28" s="41"/>
-      <c r="J28" s="14"/>
-    </row>
-    <row r="29" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="51" t="s">
+      <c r="H29" s="21">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J29" s="87">
+        <v>1</v>
+      </c>
+      <c r="K29" s="87"/>
+      <c r="L29" s="87"/>
+    </row>
+    <row r="30" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="79" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="E30" s="70">
+        <v>46178</v>
+      </c>
+      <c r="F30" s="67">
+        <v>46180</v>
+      </c>
+      <c r="G30" s="69"/>
+      <c r="H30" s="30">
+        <v>3</v>
+      </c>
+      <c r="J30" s="86">
+        <v>3</v>
+      </c>
+      <c r="K30" s="86"/>
+      <c r="L30" s="86"/>
+    </row>
+    <row r="31" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="63" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="E31" s="73">
+        <v>46180</v>
+      </c>
+      <c r="F31" s="67"/>
+      <c r="G31" s="69">
+        <v>0.875</v>
+      </c>
+      <c r="H31" s="30">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J31" s="86">
+        <v>4</v>
+      </c>
+      <c r="K31" s="86"/>
+      <c r="L31" s="86"/>
+    </row>
+    <row r="32" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="E29" s="52">
-        <v>46173</v>
-      </c>
-      <c r="H29" s="41">
-        <v>6</v>
-      </c>
-      <c r="J29" s="14"/>
-    </row>
-    <row r="30" spans="2:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" s="26">
-        <v>0.1</v>
-      </c>
-      <c r="E30" s="53">
-        <v>46173</v>
-      </c>
-      <c r="F30" s="28"/>
-      <c r="G30" s="29">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H30" s="30">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J30" s="14"/>
-    </row>
-    <row r="31" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="19">
-        <v>0.1</v>
-      </c>
-      <c r="E31" s="20">
-        <v>46178</v>
-      </c>
-      <c r="F31" s="21">
+      <c r="C32" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="13">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E32" s="70">
         <v>46180</v>
       </c>
-      <c r="G31" s="22"/>
-      <c r="H31" s="23">
-        <v>3</v>
-      </c>
-      <c r="J31" s="14"/>
-    </row>
-    <row r="32" spans="2:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="15">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="E32" s="5">
-        <v>46180</v>
-      </c>
-      <c r="H32" s="41"/>
+      <c r="F32" s="67">
+        <v>46188</v>
+      </c>
+      <c r="G32" s="69"/>
+      <c r="H32" s="30"/>
       <c r="I32" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J32" s="14"/>
-      <c r="M32" s="16"/>
-    </row>
-    <row r="33" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="47" t="s">
+      <c r="J32" s="2"/>
+      <c r="K32" s="86">
+        <v>5</v>
+      </c>
+      <c r="L32" s="86"/>
+      <c r="M32" s="14"/>
+    </row>
+    <row r="33" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B33" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="23">
         <v>0.15</v>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="24">
         <v>46180</v>
       </c>
-      <c r="F33" s="28"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="30"/>
-      <c r="J33" s="14"/>
-    </row>
-    <row r="34" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="44" t="s">
+      <c r="F33" s="25"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="27"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="86">
+        <v>6</v>
+      </c>
+      <c r="L33" s="86"/>
+    </row>
+    <row r="34" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="55">
+      <c r="D34" s="13">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E34" s="56">
+      <c r="E34" s="65">
         <v>46181</v>
       </c>
-      <c r="F34" s="21"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="23"/>
-      <c r="J34" s="14"/>
-    </row>
-    <row r="35" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="40" t="s">
+      <c r="F34" s="67"/>
+      <c r="G34" s="69"/>
+      <c r="H34" s="30"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="86">
+        <v>8</v>
+      </c>
+      <c r="L34" s="86"/>
+    </row>
+    <row r="35" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="29" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -1846,160 +2031,187 @@
       <c r="D35" s="12">
         <v>0.1</v>
       </c>
-      <c r="E35" s="52">
+      <c r="E35" s="34">
         <v>46181</v>
       </c>
       <c r="F35" s="6">
         <v>46187</v>
       </c>
-      <c r="H35" s="41"/>
+      <c r="H35" s="30"/>
       <c r="I35" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J35" s="14"/>
-    </row>
-    <row r="36" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="47" t="s">
+      <c r="J35" s="86"/>
+      <c r="L35" s="86">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B36" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C36" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D36" s="26">
+      <c r="D36" s="23">
         <v>0.2</v>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="24">
         <v>46186</v>
       </c>
-      <c r="F36" s="28"/>
-      <c r="G36" s="29">
+      <c r="F36" s="25"/>
+      <c r="G36" s="26">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H36" s="30">
+      <c r="H36" s="27">
         <v>4.5</v>
       </c>
-      <c r="J36" s="14"/>
-    </row>
-    <row r="37" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="19">
-        <v>0.2</v>
-      </c>
-      <c r="E37" s="20">
+      <c r="J36" s="86"/>
+      <c r="L36" s="86">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B37" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="E37" s="18">
         <v>46188</v>
       </c>
-      <c r="F37" s="21"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="23">
-        <v>6.7</v>
-      </c>
-      <c r="J37" s="14"/>
-      <c r="O37" s="16"/>
-    </row>
-    <row r="38" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>33</v>
+      <c r="F37" s="19">
+        <v>46194</v>
+      </c>
+      <c r="G37" s="20"/>
+      <c r="H37" s="21"/>
+      <c r="J37" s="86"/>
+      <c r="L37" s="86">
+        <v>12</v>
+      </c>
+      <c r="O37" s="14"/>
+    </row>
+    <row r="38" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="63" t="s">
+        <v>17</v>
       </c>
       <c r="D38" s="12">
-        <v>0.15</v>
-      </c>
-      <c r="E38" s="5">
-        <v>46188</v>
-      </c>
-      <c r="F38" s="6">
-        <v>46194</v>
-      </c>
-      <c r="H38" s="41"/>
+        <v>0.25</v>
+      </c>
+      <c r="E38" s="70">
+        <v>46189</v>
+      </c>
+      <c r="F38" s="67"/>
+      <c r="G38" s="69"/>
+      <c r="H38" s="30">
+        <v>1.6</v>
+      </c>
       <c r="I38" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>17</v>
+      <c r="L38" s="87">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B39" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="63" t="s">
+        <v>24</v>
       </c>
       <c r="D39" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="E39" s="5">
-        <v>46189</v>
-      </c>
-      <c r="H39" s="41">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="40" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="31" t="s">
+        <v>0.2</v>
+      </c>
+      <c r="E39" s="70">
+        <v>46194</v>
+      </c>
+      <c r="F39" s="67"/>
+      <c r="G39" s="69"/>
+      <c r="H39" s="30"/>
+      <c r="M39" s="87">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="E40" s="18">
+        <v>46196</v>
+      </c>
+      <c r="F40" s="19"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="21">
+        <v>6.7</v>
+      </c>
+      <c r="M40" s="87">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="26">
-        <v>0.2</v>
-      </c>
-      <c r="E40" s="27">
-        <v>46194</v>
-      </c>
-      <c r="F40" s="28"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="30"/>
-    </row>
-    <row r="41" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="19"/>
-      <c r="E41" s="20">
+      <c r="D41" s="12"/>
+      <c r="E41" s="70">
         <v>46197</v>
       </c>
-      <c r="F41" s="21"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="23"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="30"/>
       <c r="I41" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="24" t="s">
+      <c r="M41" s="87">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B42" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D42" s="26">
+      <c r="D42" s="23">
         <v>0.05</v>
       </c>
-      <c r="E42" s="27">
+      <c r="E42" s="24">
         <v>46201</v>
       </c>
-      <c r="F42" s="28"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="30">
+      <c r="F42" s="25"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="27">
         <v>7</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="M42" s="87">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B43" s="3"/>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B44" s="3"/>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B45" s="3"/>
     </row>
   </sheetData>

--- a/CalendarioEvaluaciones.xlsx
+++ b/CalendarioEvaluaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09508BD7-B20A-444C-8C21-B0B34F4B80E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F792590A-D14A-44A3-B07C-15E92A6BCE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -587,9 +587,6 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -691,9 +688,6 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -724,6 +718,12 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1241,7 +1241,7 @@
     <col min="7" max="7" width="14.85546875" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.28515625" style="2"/>
-    <col min="10" max="10" width="9.28515625" style="87"/>
+    <col min="10" max="10" width="9.28515625" style="85"/>
     <col min="11" max="16384" width="9.28515625" style="2"/>
   </cols>
   <sheetData>
@@ -1267,575 +1267,575 @@
       <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="82"/>
-    </row>
-    <row r="2" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J1" s="80"/>
+    </row>
+    <row r="2" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="37">
+      <c r="D2" s="36">
         <v>0.05</v>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="37">
         <v>46088</v>
       </c>
-      <c r="F2" s="39">
+      <c r="F2" s="38">
         <v>46091</v>
       </c>
-      <c r="G2" s="40"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="42" t="s">
+      <c r="G2" s="39"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="83"/>
-    </row>
-    <row r="3" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="J2" s="81"/>
+    </row>
+    <row r="3" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="44">
+      <c r="D3" s="43">
         <v>0.05</v>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="44">
         <v>46089</v>
       </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="48">
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="47">
         <v>1</v>
       </c>
-      <c r="J3" s="83"/>
-    </row>
-    <row r="4" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J3" s="81"/>
+    </row>
+    <row r="4" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="37">
+      <c r="D4" s="36">
         <v>0.15</v>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="37">
         <v>46095</v>
       </c>
-      <c r="F4" s="39"/>
-      <c r="G4" s="40">
+      <c r="F4" s="38"/>
+      <c r="G4" s="39">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="40">
         <v>1</v>
       </c>
-      <c r="I4" s="42" t="s">
+      <c r="I4" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="83"/>
-    </row>
-    <row r="5" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="J4" s="81"/>
+    </row>
+    <row r="5" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="43">
         <v>0.1</v>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="44">
         <v>46096</v>
       </c>
-      <c r="F5" s="46"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="48"/>
-      <c r="J5" s="83"/>
-    </row>
-    <row r="6" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F5" s="45"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="47"/>
+      <c r="J5" s="81"/>
+    </row>
+    <row r="6" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="36">
         <v>0.1</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="37">
         <v>46097</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="38">
         <v>46110</v>
       </c>
-      <c r="G6" s="40"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="42" t="s">
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="83"/>
-    </row>
-    <row r="7" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="J6" s="81"/>
+    </row>
+    <row r="7" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="45">
+      <c r="D7" s="43"/>
+      <c r="E7" s="44">
         <v>46099</v>
       </c>
-      <c r="F7" s="46"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="48"/>
-      <c r="J7" s="83"/>
-    </row>
-    <row r="8" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="49" t="s">
+      <c r="F7" s="45"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="47"/>
+      <c r="J7" s="81"/>
+    </row>
+    <row r="8" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="50">
         <v>0.1</v>
       </c>
-      <c r="E8" s="52">
+      <c r="E8" s="51">
         <v>46104</v>
       </c>
-      <c r="F8" s="53"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="55" t="s">
+      <c r="F8" s="52"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="42" t="s">
+      <c r="I8" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="83"/>
-    </row>
-    <row r="9" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J8" s="81"/>
+    </row>
+    <row r="9" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="36">
         <v>0.1</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="37">
         <v>46118</v>
       </c>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40">
+      <c r="F9" s="38"/>
+      <c r="G9" s="39">
         <v>0.875</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="40">
         <v>1</v>
       </c>
-      <c r="I9" s="42" t="s">
+      <c r="I9" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="83"/>
-    </row>
-    <row r="10" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J9" s="81"/>
+    </row>
+    <row r="10" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="56">
+      <c r="D10" s="55">
         <v>0.1</v>
       </c>
-      <c r="E10" s="57">
+      <c r="E10" s="56">
         <v>46118</v>
       </c>
-      <c r="F10" s="58">
+      <c r="F10" s="57">
         <v>46124</v>
       </c>
-      <c r="G10" s="59"/>
-      <c r="H10" s="60"/>
-      <c r="J10" s="83"/>
-    </row>
-    <row r="11" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G10" s="58"/>
+      <c r="H10" s="59"/>
+      <c r="J10" s="81"/>
+    </row>
+    <row r="11" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="C11" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="56">
+      <c r="D11" s="55">
         <v>0.15</v>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="63">
         <v>46121</v>
       </c>
-      <c r="F11" s="66"/>
-      <c r="G11" s="68">
+      <c r="F11" s="65"/>
+      <c r="G11" s="67">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H11" s="60">
+      <c r="H11" s="59">
         <v>2</v>
       </c>
-      <c r="J11" s="83"/>
-    </row>
-    <row r="12" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="J11" s="81"/>
+    </row>
+    <row r="12" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B12" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="43">
         <v>0.15</v>
       </c>
-      <c r="E12" s="45">
+      <c r="E12" s="44">
         <v>46124</v>
       </c>
-      <c r="F12" s="46"/>
-      <c r="G12" s="47">
+      <c r="F12" s="45"/>
+      <c r="G12" s="46">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H12" s="48">
+      <c r="H12" s="47">
         <v>2</v>
       </c>
-      <c r="J12" s="83"/>
-    </row>
-    <row r="13" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J12" s="81"/>
+    </row>
+    <row r="13" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="37">
+      <c r="D13" s="36">
         <v>0.15</v>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="37">
         <v>46125</v>
       </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="40">
+      <c r="F13" s="38"/>
+      <c r="G13" s="39">
         <v>0.875</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="40">
         <v>1</v>
       </c>
-      <c r="I13" s="42" t="s">
+      <c r="I13" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="84"/>
-    </row>
-    <row r="14" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="J13" s="82"/>
+    </row>
+    <row r="14" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B14" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="43">
         <v>0.1</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="44">
         <v>46128</v>
       </c>
-      <c r="F14" s="46">
+      <c r="F14" s="45">
         <v>46131</v>
       </c>
-      <c r="G14" s="47"/>
-      <c r="H14" s="48"/>
-      <c r="J14" s="84"/>
-    </row>
-    <row r="15" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G14" s="46"/>
+      <c r="H14" s="47"/>
+      <c r="J14" s="82"/>
+    </row>
+    <row r="15" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="36">
         <v>0.2</v>
       </c>
-      <c r="E15" s="38">
+      <c r="E15" s="37">
         <v>46132</v>
       </c>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="41">
+      <c r="F15" s="38"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40">
         <v>3</v>
       </c>
-      <c r="I15" s="42" t="s">
+      <c r="I15" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="J15" s="84"/>
-    </row>
-    <row r="16" spans="2:10" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J15" s="82"/>
+    </row>
+    <row r="16" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="56">
+      <c r="D16" s="55">
         <v>0.15</v>
       </c>
-      <c r="E16" s="57">
+      <c r="E16" s="56">
         <v>46135</v>
       </c>
-      <c r="F16" s="58">
+      <c r="F16" s="57">
         <v>46145</v>
       </c>
-      <c r="G16" s="59"/>
-      <c r="H16" s="60"/>
-      <c r="J16" s="84"/>
-    </row>
-    <row r="17" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G16" s="58"/>
+      <c r="H16" s="59"/>
+      <c r="J16" s="82"/>
+    </row>
+    <row r="17" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B17" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="43" t="s">
+      <c r="C17" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="44">
+      <c r="D17" s="43">
         <v>0.1</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="44">
         <v>46137</v>
       </c>
-      <c r="F17" s="46"/>
-      <c r="G17" s="47">
+      <c r="F17" s="45"/>
+      <c r="G17" s="46">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H17" s="48">
+      <c r="H17" s="47">
         <v>1.3</v>
       </c>
-      <c r="J17" s="84"/>
-    </row>
-    <row r="18" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="49" t="s">
+      <c r="J17" s="82"/>
+    </row>
+    <row r="18" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="50">
         <v>0.15</v>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="51">
         <v>46145</v>
       </c>
-      <c r="F18" s="53"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="42" t="s">
+      <c r="F18" s="52"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="J18" s="85"/>
-    </row>
-    <row r="19" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J18" s="83"/>
+    </row>
+    <row r="19" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="36">
         <v>0.1</v>
       </c>
-      <c r="E19" s="38">
+      <c r="E19" s="37">
         <v>46146</v>
       </c>
-      <c r="F19" s="39"/>
-      <c r="G19" s="40">
+      <c r="F19" s="38"/>
+      <c r="G19" s="39">
         <v>0.875</v>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="40">
         <v>2</v>
       </c>
-      <c r="I19" s="42" t="s">
+      <c r="I19" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="J19" s="85"/>
-    </row>
-    <row r="20" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="J19" s="83"/>
+    </row>
+    <row r="20" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B20" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="44">
+      <c r="D20" s="43">
         <v>0.05</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="44">
         <v>46151</v>
       </c>
-      <c r="F20" s="46"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="48"/>
-      <c r="J20" s="84"/>
-    </row>
-    <row r="21" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F20" s="45"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="47"/>
+      <c r="J20" s="82"/>
+    </row>
+    <row r="21" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="37">
+      <c r="D21" s="36">
         <v>0.15</v>
       </c>
-      <c r="E21" s="38">
+      <c r="E21" s="37">
         <v>46153</v>
       </c>
-      <c r="F21" s="39">
+      <c r="F21" s="38">
         <v>46159</v>
       </c>
-      <c r="G21" s="40"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="42" t="s">
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="J21" s="85"/>
-    </row>
-    <row r="22" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J21" s="83"/>
+    </row>
+    <row r="22" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="42" t="s">
+      <c r="C22" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="56">
+      <c r="D22" s="55">
         <v>0.1</v>
       </c>
-      <c r="E22" s="57">
+      <c r="E22" s="56">
         <v>46156</v>
       </c>
-      <c r="F22" s="58">
+      <c r="F22" s="57">
         <v>46159</v>
       </c>
-      <c r="G22" s="59"/>
-      <c r="H22" s="60"/>
-      <c r="J22" s="85"/>
-    </row>
-    <row r="23" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G22" s="58"/>
+      <c r="H22" s="59"/>
+      <c r="J22" s="83"/>
+    </row>
+    <row r="23" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="62" t="s">
+      <c r="C23" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="56">
+      <c r="D23" s="55">
         <v>0.1</v>
       </c>
-      <c r="E23" s="64">
+      <c r="E23" s="63">
         <v>46157</v>
       </c>
-      <c r="F23" s="66">
+      <c r="F23" s="65">
         <v>46159</v>
       </c>
-      <c r="G23" s="68"/>
-      <c r="H23" s="60">
+      <c r="G23" s="67"/>
+      <c r="H23" s="59">
         <v>2</v>
       </c>
-      <c r="J23" s="85"/>
-    </row>
-    <row r="24" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="J23" s="83"/>
+    </row>
+    <row r="24" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B24" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="43" t="s">
+      <c r="C24" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="44">
+      <c r="D24" s="43">
         <v>0.2</v>
       </c>
-      <c r="E24" s="45">
+      <c r="E24" s="44">
         <v>46158</v>
       </c>
-      <c r="F24" s="46"/>
-      <c r="G24" s="47">
+      <c r="F24" s="45"/>
+      <c r="G24" s="46">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H24" s="48">
+      <c r="H24" s="47">
         <v>3</v>
       </c>
-      <c r="J24" s="85"/>
-    </row>
-    <row r="25" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J24" s="83"/>
+    </row>
+    <row r="25" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="37">
+      <c r="D25" s="36">
         <v>0.2</v>
       </c>
-      <c r="E25" s="61">
+      <c r="E25" s="60">
         <v>46167</v>
       </c>
-      <c r="F25" s="39"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="41">
+      <c r="F25" s="38"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40">
         <v>4.5</v>
       </c>
-      <c r="J25" s="85"/>
+      <c r="J25" s="83"/>
     </row>
     <row r="26" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="42"/>
+      <c r="A26" s="41"/>
       <c r="B26" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="62" t="s">
+      <c r="C26" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="56">
+      <c r="D26" s="55">
         <v>0.1</v>
       </c>
-      <c r="E26" s="64">
+      <c r="E26" s="63">
         <v>46170</v>
       </c>
-      <c r="F26" s="66"/>
-      <c r="G26" s="68">
+      <c r="F26" s="65"/>
+      <c r="G26" s="67">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H26" s="60"/>
+      <c r="H26" s="59"/>
       <c r="I26" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J26" s="86"/>
-    </row>
-    <row r="27" spans="1:20" s="42" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J26" s="84"/>
+    </row>
+    <row r="27" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2"/>
       <c r="B27" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="63" t="s">
+      <c r="C27" s="62" t="s">
         <v>34</v>
       </c>
       <c r="D27" s="12">
         <v>0.25</v>
       </c>
-      <c r="E27" s="70">
+      <c r="E27" s="69">
         <v>46171</v>
       </c>
-      <c r="F27" s="67">
+      <c r="F27" s="66">
         <v>46182</v>
       </c>
-      <c r="G27" s="69"/>
+      <c r="G27" s="68"/>
       <c r="H27" s="30"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="87">
+      <c r="K27" s="85">
         <v>7</v>
       </c>
-      <c r="L27" s="87"/>
+      <c r="L27" s="85"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -1846,139 +1846,139 @@
       <c r="T27" s="2"/>
     </row>
     <row r="28" spans="1:20" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B28" s="81" t="s">
+      <c r="B28" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="63" t="s">
+      <c r="C28" s="62" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="12">
         <v>0.05</v>
       </c>
-      <c r="E28" s="65">
+      <c r="E28" s="64">
         <v>46173</v>
       </c>
-      <c r="F28" s="67">
+      <c r="F28" s="66">
         <v>46180</v>
       </c>
-      <c r="G28" s="69"/>
+      <c r="G28" s="68"/>
       <c r="H28" s="30">
         <v>6</v>
       </c>
-      <c r="J28" s="87">
+      <c r="J28" s="85">
         <v>2</v>
       </c>
-      <c r="K28" s="87"/>
-      <c r="L28" s="87"/>
-    </row>
-    <row r="29" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="74" t="s">
+      <c r="K28" s="85"/>
+      <c r="L28" s="85"/>
+    </row>
+    <row r="29" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="36">
         <v>0.1</v>
       </c>
-      <c r="E29" s="35">
+      <c r="E29" s="87">
         <v>46176</v>
       </c>
-      <c r="F29" s="19"/>
-      <c r="G29" s="20">
+      <c r="F29" s="38"/>
+      <c r="G29" s="39">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H29" s="21">
+      <c r="H29" s="40">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J29" s="87">
+      <c r="J29" s="81">
         <v>1</v>
       </c>
-      <c r="K29" s="87"/>
-      <c r="L29" s="87"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="81"/>
     </row>
     <row r="30" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="79" t="s">
+      <c r="B30" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="63" t="s">
+      <c r="C30" s="62" t="s">
         <v>27</v>
       </c>
       <c r="D30" s="12">
         <v>0.1</v>
       </c>
-      <c r="E30" s="70">
+      <c r="E30" s="69">
         <v>46178</v>
       </c>
-      <c r="F30" s="67">
+      <c r="F30" s="66">
         <v>46180</v>
       </c>
-      <c r="G30" s="69"/>
+      <c r="G30" s="68"/>
       <c r="H30" s="30">
         <v>3</v>
       </c>
-      <c r="J30" s="86">
+      <c r="J30" s="84">
         <v>3</v>
       </c>
-      <c r="K30" s="86"/>
-      <c r="L30" s="86"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
     </row>
     <row r="31" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="75" t="s">
+      <c r="B31" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="63" t="s">
+      <c r="C31" s="62" t="s">
         <v>18</v>
       </c>
       <c r="D31" s="12">
         <v>0.15</v>
       </c>
-      <c r="E31" s="73">
+      <c r="E31" s="72">
         <v>46180</v>
       </c>
-      <c r="F31" s="67"/>
-      <c r="G31" s="69">
+      <c r="F31" s="66"/>
+      <c r="G31" s="68">
         <v>0.875</v>
       </c>
       <c r="H31" s="30">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J31" s="86">
+      <c r="J31" s="84">
         <v>4</v>
       </c>
-      <c r="K31" s="86"/>
-      <c r="L31" s="86"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
     </row>
     <row r="32" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="76" t="s">
+      <c r="B32" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="63" t="s">
+      <c r="C32" s="62" t="s">
         <v>15</v>
       </c>
       <c r="D32" s="13">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E32" s="70">
+      <c r="E32" s="69">
         <v>46180</v>
       </c>
-      <c r="F32" s="67">
+      <c r="F32" s="66">
         <v>46188</v>
       </c>
-      <c r="G32" s="69"/>
+      <c r="G32" s="68"/>
       <c r="H32" s="30"/>
       <c r="I32" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J32" s="2"/>
-      <c r="K32" s="86">
+      <c r="K32" s="84">
         <v>5</v>
       </c>
-      <c r="L32" s="86"/>
+      <c r="L32" s="84"/>
       <c r="M32" s="14"/>
     </row>
     <row r="33" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="77" t="s">
+      <c r="B33" s="75" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="22" t="s">
@@ -1994,32 +1994,32 @@
       <c r="G33" s="26"/>
       <c r="H33" s="27"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="86">
+      <c r="K33" s="84">
         <v>6</v>
       </c>
-      <c r="L33" s="86"/>
+      <c r="L33" s="84"/>
     </row>
     <row r="34" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="72" t="s">
+      <c r="B34" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="63" t="s">
+      <c r="C34" s="62" t="s">
         <v>16</v>
       </c>
       <c r="D34" s="13">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E34" s="65">
+      <c r="E34" s="64">
         <v>46181</v>
       </c>
-      <c r="F34" s="67"/>
-      <c r="G34" s="69"/>
+      <c r="F34" s="66"/>
+      <c r="G34" s="68"/>
       <c r="H34" s="30"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="86">
+      <c r="K34" s="84">
         <v>8</v>
       </c>
-      <c r="L34" s="86"/>
+      <c r="L34" s="84"/>
     </row>
     <row r="35" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="29" t="s">
@@ -2041,8 +2041,8 @@
       <c r="I35" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J35" s="86"/>
-      <c r="L35" s="86">
+      <c r="J35" s="84"/>
+      <c r="L35" s="84">
         <v>10</v>
       </c>
     </row>
@@ -2066,8 +2066,8 @@
       <c r="H36" s="27">
         <v>4.5</v>
       </c>
-      <c r="J36" s="86"/>
-      <c r="L36" s="86">
+      <c r="J36" s="84"/>
+      <c r="L36" s="84">
         <v>9</v>
       </c>
     </row>
@@ -2089,8 +2089,8 @@
       </c>
       <c r="G37" s="20"/>
       <c r="H37" s="21"/>
-      <c r="J37" s="86"/>
-      <c r="L37" s="86">
+      <c r="J37" s="84"/>
+      <c r="L37" s="84">
         <v>12</v>
       </c>
       <c r="O37" s="14"/>
@@ -2099,49 +2099,49 @@
       <c r="B38" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="63" t="s">
+      <c r="C38" s="62" t="s">
         <v>17</v>
       </c>
       <c r="D38" s="12">
         <v>0.25</v>
       </c>
-      <c r="E38" s="70">
+      <c r="E38" s="69">
         <v>46189</v>
       </c>
-      <c r="F38" s="67"/>
-      <c r="G38" s="69"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="68"/>
       <c r="H38" s="30">
         <v>1.6</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L38" s="87">
+      <c r="L38" s="85">
         <v>11</v>
       </c>
     </row>
     <row r="39" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B39" s="71" t="s">
+      <c r="B39" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="63" t="s">
+      <c r="C39" s="62" t="s">
         <v>24</v>
       </c>
       <c r="D39" s="12">
         <v>0.2</v>
       </c>
-      <c r="E39" s="70">
+      <c r="E39" s="69">
         <v>46194</v>
       </c>
-      <c r="F39" s="67"/>
-      <c r="G39" s="69"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="68"/>
       <c r="H39" s="30"/>
-      <c r="M39" s="87">
+      <c r="M39" s="85">
         <v>13</v>
       </c>
     </row>
     <row r="40" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="78" t="s">
+      <c r="B40" s="76" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="16" t="s">
@@ -2158,33 +2158,33 @@
       <c r="H40" s="21">
         <v>6.7</v>
       </c>
-      <c r="M40" s="87">
+      <c r="M40" s="85">
         <v>14</v>
       </c>
     </row>
     <row r="41" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="79" t="s">
+      <c r="B41" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="63" t="s">
+      <c r="C41" s="62" t="s">
         <v>29</v>
       </c>
       <c r="D41" s="12"/>
-      <c r="E41" s="70">
+      <c r="E41" s="69">
         <v>46197</v>
       </c>
-      <c r="F41" s="67"/>
-      <c r="G41" s="69"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="68"/>
       <c r="H41" s="30"/>
       <c r="I41" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M41" s="87">
+      <c r="M41" s="85">
         <v>15</v>
       </c>
     </row>
     <row r="42" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B42" s="80" t="s">
+      <c r="B42" s="78" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="22" t="s">
@@ -2201,7 +2201,7 @@
       <c r="H42" s="27">
         <v>7</v>
       </c>
-      <c r="M42" s="87">
+      <c r="M42" s="85">
         <v>16</v>
       </c>
     </row>

--- a/CalendarioEvaluaciones.xlsx
+++ b/CalendarioEvaluaciones.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F792590A-D14A-44A3-B07C-15E92A6BCE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9520B3BE-A95A-433F-90FD-6806A102A86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -32,9 +32,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -493,7 +490,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -569,9 +566,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -579,9 +573,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -657,41 +648,12 @@
     <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -705,9 +667,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -722,6 +681,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1229,7 +1200,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="26.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="2"/>
@@ -1241,7 +1212,7 @@
     <col min="7" max="7" width="14.85546875" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.28515625" style="2"/>
-    <col min="10" max="10" width="9.28515625" style="85"/>
+    <col min="10" max="10" width="9.28515625" style="71"/>
     <col min="11" max="16384" width="9.28515625" style="2"/>
   </cols>
   <sheetData>
@@ -1267,718 +1238,706 @@
       <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="80"/>
-    </row>
-    <row r="2" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J1" s="66"/>
+    </row>
+    <row r="2" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="36">
+      <c r="D2" s="34">
         <v>0.05</v>
       </c>
-      <c r="E2" s="37">
+      <c r="E2" s="35">
         <v>46088</v>
       </c>
-      <c r="F2" s="38">
+      <c r="F2" s="36">
         <v>46091</v>
       </c>
-      <c r="G2" s="39"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="41" t="s">
+      <c r="G2" s="37"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="81"/>
-    </row>
-    <row r="3" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="31" t="s">
+      <c r="J2" s="67"/>
+    </row>
+    <row r="3" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="43">
+      <c r="D3" s="41">
         <v>0.05</v>
       </c>
-      <c r="E3" s="44">
+      <c r="E3" s="42">
         <v>46089</v>
       </c>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="47">
+      <c r="F3" s="43"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="45">
         <v>1</v>
       </c>
-      <c r="J3" s="81"/>
-    </row>
-    <row r="4" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J3" s="67"/>
+    </row>
+    <row r="4" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="34">
         <v>0.15</v>
       </c>
-      <c r="E4" s="37">
+      <c r="E4" s="35">
         <v>46095</v>
       </c>
-      <c r="F4" s="38"/>
-      <c r="G4" s="39">
+      <c r="F4" s="36"/>
+      <c r="G4" s="37">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H4" s="40">
+      <c r="H4" s="38">
         <v>1</v>
       </c>
-      <c r="I4" s="41" t="s">
+      <c r="I4" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="81"/>
-    </row>
-    <row r="5" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="31" t="s">
+      <c r="J4" s="67"/>
+    </row>
+    <row r="5" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="41">
         <v>0.1</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="42">
         <v>46096</v>
       </c>
-      <c r="F5" s="45"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="47"/>
-      <c r="J5" s="81"/>
-    </row>
-    <row r="6" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F5" s="43"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
+      <c r="J5" s="67"/>
+    </row>
+    <row r="6" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="34">
         <v>0.1</v>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="35">
         <v>46097</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="36">
         <v>46110</v>
       </c>
-      <c r="G6" s="39"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="41" t="s">
+      <c r="G6" s="37"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="81"/>
-    </row>
-    <row r="7" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="31" t="s">
+      <c r="J6" s="67"/>
+    </row>
+    <row r="7" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="43"/>
-      <c r="E7" s="44">
+      <c r="D7" s="41"/>
+      <c r="E7" s="42">
         <v>46099</v>
       </c>
-      <c r="F7" s="45"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47"/>
-      <c r="J7" s="81"/>
-    </row>
-    <row r="8" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="48" t="s">
+      <c r="F7" s="43"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="45"/>
+      <c r="J7" s="67"/>
+    </row>
+    <row r="8" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="48">
         <v>0.1</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="49">
         <v>46104</v>
       </c>
-      <c r="F8" s="52"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="54" t="s">
+      <c r="F8" s="50"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="41" t="s">
+      <c r="I8" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="81"/>
-    </row>
-    <row r="9" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J8" s="67"/>
+    </row>
+    <row r="9" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="34">
         <v>0.1</v>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="35">
         <v>46118</v>
       </c>
-      <c r="F9" s="38"/>
-      <c r="G9" s="39">
+      <c r="F9" s="36"/>
+      <c r="G9" s="37">
         <v>0.875</v>
       </c>
-      <c r="H9" s="40">
+      <c r="H9" s="38">
         <v>1</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="81"/>
-    </row>
-    <row r="10" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="32" t="s">
+      <c r="J9" s="67"/>
+    </row>
+    <row r="10" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="55">
+      <c r="D10" s="53">
         <v>0.1</v>
       </c>
-      <c r="E10" s="56">
+      <c r="E10" s="54">
         <v>46118</v>
       </c>
-      <c r="F10" s="57">
+      <c r="F10" s="55">
         <v>46124</v>
       </c>
-      <c r="G10" s="58"/>
-      <c r="H10" s="59"/>
-      <c r="J10" s="81"/>
-    </row>
-    <row r="11" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="32" t="s">
+      <c r="G10" s="56"/>
+      <c r="H10" s="57"/>
+      <c r="J10" s="67"/>
+    </row>
+    <row r="11" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="55">
+      <c r="D11" s="53">
         <v>0.15</v>
       </c>
-      <c r="E11" s="63">
+      <c r="E11" s="54">
         <v>46121</v>
       </c>
-      <c r="F11" s="65"/>
-      <c r="G11" s="67">
+      <c r="F11" s="55"/>
+      <c r="G11" s="56">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H11" s="59">
+      <c r="H11" s="57">
         <v>2</v>
       </c>
-      <c r="J11" s="81"/>
-    </row>
-    <row r="12" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="31" t="s">
+      <c r="J11" s="67"/>
+    </row>
+    <row r="12" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="41">
         <v>0.15</v>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="42">
         <v>46124</v>
       </c>
-      <c r="F12" s="45"/>
-      <c r="G12" s="46">
+      <c r="F12" s="43"/>
+      <c r="G12" s="44">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H12" s="47">
+      <c r="H12" s="45">
         <v>2</v>
       </c>
-      <c r="J12" s="81"/>
-    </row>
-    <row r="13" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J12" s="67"/>
+    </row>
+    <row r="13" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="34">
         <v>0.15</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="35">
         <v>46125</v>
       </c>
-      <c r="F13" s="38"/>
-      <c r="G13" s="39">
+      <c r="F13" s="36"/>
+      <c r="G13" s="37">
         <v>0.875</v>
       </c>
-      <c r="H13" s="40">
+      <c r="H13" s="38">
         <v>1</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="82"/>
-    </row>
-    <row r="14" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="31" t="s">
+      <c r="J13" s="68"/>
+    </row>
+    <row r="14" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="41">
         <v>0.1</v>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="42">
         <v>46128</v>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="43">
         <v>46131</v>
       </c>
-      <c r="G14" s="46"/>
-      <c r="H14" s="47"/>
-      <c r="J14" s="82"/>
-    </row>
-    <row r="15" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G14" s="44"/>
+      <c r="H14" s="45"/>
+      <c r="J14" s="68"/>
+    </row>
+    <row r="15" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="34">
         <v>0.2</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="35">
         <v>46132</v>
       </c>
-      <c r="F15" s="38"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="40">
+      <c r="F15" s="36"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="38">
         <v>3</v>
       </c>
-      <c r="I15" s="41" t="s">
+      <c r="I15" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="J15" s="82"/>
-    </row>
-    <row r="16" spans="2:10" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="32" t="s">
+      <c r="J15" s="68"/>
+    </row>
+    <row r="16" spans="2:10" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="53">
         <v>0.15</v>
       </c>
-      <c r="E16" s="56">
+      <c r="E16" s="54">
         <v>46135</v>
       </c>
-      <c r="F16" s="57">
+      <c r="F16" s="55">
         <v>46145</v>
       </c>
-      <c r="G16" s="58"/>
-      <c r="H16" s="59"/>
-      <c r="J16" s="82"/>
-    </row>
-    <row r="17" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="31" t="s">
+      <c r="G16" s="56"/>
+      <c r="H16" s="57"/>
+      <c r="J16" s="68"/>
+    </row>
+    <row r="17" spans="1:13" s="39" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="41">
         <v>0.1</v>
       </c>
-      <c r="E17" s="44">
+      <c r="E17" s="42">
         <v>46137</v>
       </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="46">
+      <c r="F17" s="43"/>
+      <c r="G17" s="44">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H17" s="47">
+      <c r="H17" s="45">
         <v>1.3</v>
       </c>
-      <c r="J17" s="82"/>
-    </row>
-    <row r="18" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="48" t="s">
+      <c r="J17" s="68"/>
+    </row>
+    <row r="18" spans="1:13" s="39" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="49" t="s">
+      <c r="C18" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="48">
         <v>0.15</v>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="49">
         <v>46145</v>
       </c>
-      <c r="F18" s="52"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="41" t="s">
+      <c r="F18" s="50"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="J18" s="83"/>
-    </row>
-    <row r="19" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J18" s="69"/>
+    </row>
+    <row r="19" spans="1:13" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="35" t="s">
+      <c r="C19" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="34">
         <v>0.1</v>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="35">
         <v>46146</v>
       </c>
-      <c r="F19" s="38"/>
-      <c r="G19" s="39">
+      <c r="F19" s="36"/>
+      <c r="G19" s="37">
         <v>0.875</v>
       </c>
-      <c r="H19" s="40">
+      <c r="H19" s="38">
         <v>2</v>
       </c>
-      <c r="I19" s="41" t="s">
+      <c r="I19" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="J19" s="83"/>
-    </row>
-    <row r="20" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="31" t="s">
+      <c r="J19" s="69"/>
+    </row>
+    <row r="20" spans="1:13" s="39" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B20" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="41">
         <v>0.05</v>
       </c>
-      <c r="E20" s="44">
+      <c r="E20" s="42">
         <v>46151</v>
       </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="47"/>
-      <c r="J20" s="82"/>
-    </row>
-    <row r="21" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F20" s="43"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="45"/>
+      <c r="J20" s="68"/>
+    </row>
+    <row r="21" spans="1:13" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="34">
         <v>0.15</v>
       </c>
-      <c r="E21" s="37">
+      <c r="E21" s="35">
         <v>46153</v>
       </c>
-      <c r="F21" s="38">
+      <c r="F21" s="36">
         <v>46159</v>
       </c>
-      <c r="G21" s="39"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="41" t="s">
+      <c r="G21" s="37"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="J21" s="83"/>
-    </row>
-    <row r="22" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="32" t="s">
+      <c r="J21" s="69"/>
+    </row>
+    <row r="22" spans="1:13" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="55">
+      <c r="D22" s="53">
         <v>0.1</v>
       </c>
-      <c r="E22" s="56">
+      <c r="E22" s="54">
         <v>46156</v>
       </c>
-      <c r="F22" s="57">
+      <c r="F22" s="55">
         <v>46159</v>
       </c>
-      <c r="G22" s="58"/>
-      <c r="H22" s="59"/>
-      <c r="J22" s="83"/>
-    </row>
-    <row r="23" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="32" t="s">
+      <c r="G22" s="56"/>
+      <c r="H22" s="57"/>
+      <c r="J22" s="69"/>
+    </row>
+    <row r="23" spans="1:13" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="55">
+      <c r="D23" s="53">
         <v>0.1</v>
       </c>
-      <c r="E23" s="63">
+      <c r="E23" s="54">
         <v>46157</v>
       </c>
-      <c r="F23" s="65">
+      <c r="F23" s="55">
         <v>46159</v>
       </c>
-      <c r="G23" s="67"/>
-      <c r="H23" s="59">
+      <c r="G23" s="56"/>
+      <c r="H23" s="57">
         <v>2</v>
       </c>
-      <c r="J23" s="83"/>
-    </row>
-    <row r="24" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="31" t="s">
+      <c r="J23" s="69"/>
+    </row>
+    <row r="24" spans="1:13" s="39" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="43">
+      <c r="D24" s="41">
         <v>0.2</v>
       </c>
-      <c r="E24" s="44">
+      <c r="E24" s="42">
         <v>46158</v>
       </c>
-      <c r="F24" s="45"/>
-      <c r="G24" s="46">
+      <c r="F24" s="43"/>
+      <c r="G24" s="44">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H24" s="47">
+      <c r="H24" s="45">
         <v>3</v>
       </c>
-      <c r="J24" s="83"/>
-    </row>
-    <row r="25" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J24" s="69"/>
+    </row>
+    <row r="25" spans="1:13" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="35" t="s">
+      <c r="C25" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="36">
+      <c r="D25" s="34">
         <v>0.2</v>
       </c>
-      <c r="E25" s="60">
+      <c r="E25" s="58">
         <v>46167</v>
       </c>
-      <c r="F25" s="38"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="40">
+      <c r="F25" s="36"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="38">
         <v>4.5</v>
       </c>
-      <c r="J25" s="83"/>
-    </row>
-    <row r="26" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="41"/>
-      <c r="B26" s="32" t="s">
+      <c r="J25" s="69"/>
+    </row>
+    <row r="26" spans="1:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="39"/>
+      <c r="B26" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="55">
+      <c r="D26" s="53">
         <v>0.1</v>
       </c>
-      <c r="E26" s="63">
+      <c r="E26" s="54">
         <v>46170</v>
       </c>
-      <c r="F26" s="65"/>
-      <c r="G26" s="67">
+      <c r="F26" s="55"/>
+      <c r="G26" s="56">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H26" s="59"/>
+      <c r="H26" s="57"/>
       <c r="I26" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J26" s="84"/>
-    </row>
-    <row r="27" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="2"/>
-      <c r="B27" s="32" t="s">
+      <c r="J26" s="70"/>
+    </row>
+    <row r="27" spans="1:13" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="62" t="s">
+      <c r="C27" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="53">
         <v>0.25</v>
       </c>
-      <c r="E27" s="69">
+      <c r="E27" s="54">
         <v>46171</v>
       </c>
-      <c r="F27" s="66">
+      <c r="F27" s="55">
         <v>46182</v>
       </c>
-      <c r="G27" s="68"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="85">
+      <c r="G27" s="56"/>
+      <c r="H27" s="57"/>
+      <c r="K27" s="67">
         <v>7</v>
       </c>
-      <c r="L27" s="85"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-    </row>
-    <row r="28" spans="1:20" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B28" s="79" t="s">
+      <c r="L27" s="67"/>
+    </row>
+    <row r="28" spans="1:13" s="39" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B28" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="62" t="s">
+      <c r="C28" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="53">
         <v>0.05</v>
       </c>
-      <c r="E28" s="64">
+      <c r="E28" s="75">
         <v>46173</v>
       </c>
-      <c r="F28" s="66">
+      <c r="F28" s="55">
         <v>46180</v>
       </c>
-      <c r="G28" s="68"/>
-      <c r="H28" s="30">
+      <c r="G28" s="56"/>
+      <c r="H28" s="57">
         <v>6</v>
       </c>
-      <c r="J28" s="85">
+      <c r="J28" s="67">
         <v>2</v>
       </c>
-      <c r="K28" s="85"/>
-      <c r="L28" s="85"/>
-    </row>
-    <row r="29" spans="1:20" s="41" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="86" t="s">
+      <c r="K28" s="67"/>
+      <c r="L28" s="67"/>
+    </row>
+    <row r="29" spans="1:13" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="36">
+      <c r="D29" s="34">
         <v>0.1</v>
       </c>
-      <c r="E29" s="87">
+      <c r="E29" s="73">
         <v>46176</v>
       </c>
-      <c r="F29" s="38"/>
-      <c r="G29" s="39">
+      <c r="F29" s="36"/>
+      <c r="G29" s="37">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H29" s="40">
+      <c r="H29" s="38">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J29" s="81">
+      <c r="J29" s="67">
         <v>1</v>
       </c>
-      <c r="K29" s="81"/>
-      <c r="L29" s="81"/>
-    </row>
-    <row r="30" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="77" t="s">
+      <c r="K29" s="67"/>
+      <c r="L29" s="67"/>
+    </row>
+    <row r="30" spans="1:13" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="62" t="s">
+      <c r="C30" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="53">
         <v>0.1</v>
       </c>
-      <c r="E30" s="69">
+      <c r="E30" s="54">
         <v>46178</v>
       </c>
-      <c r="F30" s="66">
+      <c r="F30" s="55">
         <v>46180</v>
       </c>
-      <c r="G30" s="68"/>
-      <c r="H30" s="30">
+      <c r="G30" s="56"/>
+      <c r="H30" s="57">
         <v>3</v>
       </c>
-      <c r="J30" s="84">
+      <c r="J30" s="69">
         <v>3</v>
       </c>
-      <c r="K30" s="84"/>
-      <c r="L30" s="84"/>
-    </row>
-    <row r="31" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="73" t="s">
+      <c r="K30" s="69"/>
+      <c r="L30" s="69"/>
+    </row>
+    <row r="31" spans="1:13" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="62" t="s">
+      <c r="C31" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="53">
         <v>0.15</v>
       </c>
-      <c r="E31" s="72">
+      <c r="E31" s="77">
         <v>46180</v>
       </c>
-      <c r="F31" s="66"/>
-      <c r="G31" s="68">
+      <c r="F31" s="55"/>
+      <c r="G31" s="56">
         <v>0.875</v>
       </c>
-      <c r="H31" s="30">
+      <c r="H31" s="57">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J31" s="84">
+      <c r="J31" s="69">
         <v>4</v>
       </c>
-      <c r="K31" s="84"/>
-      <c r="L31" s="84"/>
-    </row>
-    <row r="32" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="74" t="s">
+      <c r="K31" s="69"/>
+      <c r="L31" s="69"/>
+    </row>
+    <row r="32" spans="1:13" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="62" t="s">
+      <c r="C32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D32" s="13">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E32" s="69">
+      <c r="E32" s="5">
         <v>46180</v>
       </c>
-      <c r="F32" s="66">
+      <c r="F32" s="6">
         <v>46188</v>
       </c>
-      <c r="G32" s="68"/>
-      <c r="H32" s="30"/>
+      <c r="H32" s="29"/>
       <c r="I32" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J32" s="2"/>
-      <c r="K32" s="84">
+      <c r="K32" s="70">
         <v>5</v>
       </c>
-      <c r="L32" s="84"/>
+      <c r="L32" s="70"/>
       <c r="M32" s="14"/>
     </row>
     <row r="33" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="75" t="s">
+      <c r="B33" s="62" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="22" t="s">
@@ -1994,80 +1953,79 @@
       <c r="G33" s="26"/>
       <c r="H33" s="27"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="84">
+      <c r="K33" s="70">
         <v>6</v>
       </c>
-      <c r="L33" s="84"/>
+      <c r="L33" s="70"/>
     </row>
     <row r="34" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="71" t="s">
+      <c r="B34" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="62" t="s">
+      <c r="C34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D34" s="13">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E34" s="64">
+      <c r="E34" s="32">
         <v>46181</v>
       </c>
-      <c r="F34" s="66"/>
-      <c r="G34" s="68"/>
-      <c r="H34" s="30"/>
+      <c r="H34" s="29"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="84">
+      <c r="K34" s="70">
         <v>8</v>
       </c>
-      <c r="L34" s="84"/>
-    </row>
-    <row r="35" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="29" t="s">
+      <c r="L34" s="70"/>
+    </row>
+    <row r="35" spans="2:15" s="39" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="53">
         <v>0.1</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="75">
         <v>46181</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="55">
         <v>46187</v>
       </c>
-      <c r="H35" s="30"/>
-      <c r="I35" s="2" t="s">
+      <c r="G35" s="56"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="J35" s="84"/>
-      <c r="L35" s="84">
+      <c r="J35" s="69"/>
+      <c r="L35" s="69">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="33" t="s">
+    <row r="36" spans="2:15" s="39" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B36" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="41">
         <v>0.2</v>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="42">
         <v>46186</v>
       </c>
-      <c r="F36" s="25"/>
-      <c r="G36" s="26">
+      <c r="F36" s="43"/>
+      <c r="G36" s="44">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H36" s="27">
+      <c r="H36" s="45">
         <v>4.5</v>
       </c>
-      <c r="J36" s="84"/>
-      <c r="L36" s="84">
+      <c r="J36" s="69"/>
+      <c r="L36" s="69">
         <v>9</v>
       </c>
     </row>
@@ -2089,59 +2047,55 @@
       </c>
       <c r="G37" s="20"/>
       <c r="H37" s="21"/>
-      <c r="J37" s="84"/>
-      <c r="L37" s="84">
+      <c r="J37" s="70"/>
+      <c r="L37" s="70">
         <v>12</v>
       </c>
       <c r="O37" s="14"/>
     </row>
     <row r="38" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="32" t="s">
+      <c r="B38" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="62" t="s">
+      <c r="C38" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D38" s="12">
         <v>0.25</v>
       </c>
-      <c r="E38" s="69">
+      <c r="E38" s="5">
         <v>46189</v>
       </c>
-      <c r="F38" s="66"/>
-      <c r="G38" s="68"/>
-      <c r="H38" s="30">
+      <c r="H38" s="29">
         <v>1.6</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L38" s="85">
+      <c r="L38" s="71">
         <v>11</v>
       </c>
     </row>
     <row r="39" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B39" s="70" t="s">
+      <c r="B39" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="62" t="s">
+      <c r="C39" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D39" s="12">
         <v>0.2</v>
       </c>
-      <c r="E39" s="69">
+      <c r="E39" s="5">
         <v>46194</v>
       </c>
-      <c r="F39" s="66"/>
-      <c r="G39" s="68"/>
-      <c r="H39" s="30"/>
-      <c r="M39" s="85">
+      <c r="H39" s="29"/>
+      <c r="M39" s="71">
         <v>13</v>
       </c>
     </row>
     <row r="40" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="76" t="s">
+      <c r="B40" s="63" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="16" t="s">
@@ -2158,33 +2112,31 @@
       <c r="H40" s="21">
         <v>6.7</v>
       </c>
-      <c r="M40" s="85">
+      <c r="M40" s="71">
         <v>14</v>
       </c>
     </row>
     <row r="41" spans="2:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="77" t="s">
+      <c r="B41" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="62" t="s">
+      <c r="C41" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D41" s="12"/>
-      <c r="E41" s="69">
+      <c r="E41" s="5">
         <v>46197</v>
       </c>
-      <c r="F41" s="66"/>
-      <c r="G41" s="68"/>
-      <c r="H41" s="30"/>
+      <c r="H41" s="29"/>
       <c r="I41" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M41" s="85">
+      <c r="M41" s="71">
         <v>15</v>
       </c>
     </row>
     <row r="42" spans="2:15" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B42" s="78" t="s">
+      <c r="B42" s="65" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="22" t="s">
@@ -2201,7 +2153,7 @@
       <c r="H42" s="27">
         <v>7</v>
       </c>
-      <c r="M42" s="85">
+      <c r="M42" s="71">
         <v>16</v>
       </c>
     </row>
